--- a/data/trans_dic/Q25_A_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 40,58</t>
+          <t>16,23; 42,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,94; 43,13</t>
+          <t>21,82; 43,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 38,58</t>
+          <t>18,36; 39,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 32,6</t>
+          <t>9,69; 31,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,68; 77,82</t>
+          <t>29,64; 75,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,45; 54,56</t>
+          <t>23,16; 58,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,2; 49,05</t>
+          <t>21,6; 47,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 43,07</t>
+          <t>8,59; 42,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,97; 48,13</t>
+          <t>23,81; 48,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,39; 43,08</t>
+          <t>25,08; 43,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,07; 39,19</t>
+          <t>21,99; 38,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 30,67</t>
+          <t>11,64; 31,23</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 32,02</t>
+          <t>15,82; 31,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,17; 34,94</t>
+          <t>19,6; 35,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,84; 39,02</t>
+          <t>20,12; 39,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 30,61</t>
+          <t>12,02; 30,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,23; 73,19</t>
+          <t>34,08; 72,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,37; 56,18</t>
+          <t>30,14; 55,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,63; 50,04</t>
+          <t>19,62; 50,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,26; 37,91</t>
+          <t>16,7; 37,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,91; 37,42</t>
+          <t>21,94; 38,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,24; 39,61</t>
+          <t>25,22; 39,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,52; 38,87</t>
+          <t>22,51; 39,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,79; 30,53</t>
+          <t>16,21; 30,22</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,5; 26,64</t>
+          <t>7,56; 27,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 36,67</t>
+          <t>17,62; 35,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 34,22</t>
+          <t>14,05; 33,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 35,02</t>
+          <t>14,59; 34,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,84; 75,46</t>
+          <t>20,43; 75,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,91; 59,78</t>
+          <t>23,86; 58,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,77; 55,0</t>
+          <t>21,34; 55,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,07; 43,1</t>
+          <t>19,13; 42,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 32,5</t>
+          <t>12,57; 32,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,54; 38,78</t>
+          <t>21,92; 38,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 35,85</t>
+          <t>18,96; 36,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,51; 34,09</t>
+          <t>19,85; 34,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 34,56</t>
+          <t>14,98; 33,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,54; 33,85</t>
+          <t>17,13; 34,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,13; 30,45</t>
+          <t>12,66; 29,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 24,52</t>
+          <t>7,28; 25,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,08; 48,49</t>
+          <t>19,98; 48,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,79; 50,24</t>
+          <t>22,24; 48,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,98; 39,44</t>
+          <t>14,34; 38,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 32,52</t>
+          <t>15,99; 33,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,63; 35,0</t>
+          <t>18,93; 35,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 34,97</t>
+          <t>21,17; 35,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,15; 28,82</t>
+          <t>15,12; 29,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 25,08</t>
+          <t>12,05; 24,9</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 41,78</t>
+          <t>12,24; 40,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,59; 47,86</t>
+          <t>19,94; 47,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,32; 41,06</t>
+          <t>15,39; 44,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 40,89</t>
+          <t>7,41; 40,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,16; 61,68</t>
+          <t>23,91; 61,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 55,51</t>
+          <t>18,35; 54,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,33; 71,92</t>
+          <t>30,08; 72,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 53,59</t>
+          <t>5,09; 51,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,7; 44,17</t>
+          <t>21,47; 43,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 44,73</t>
+          <t>22,96; 45,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,0; 45,12</t>
+          <t>22,7; 45,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 36,54</t>
+          <t>9,88; 35,97</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,35; 48,28</t>
+          <t>20,37; 46,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,62; 44,77</t>
+          <t>23,06; 43,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,26; 29,85</t>
+          <t>7,99; 30,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 28,76</t>
+          <t>6,38; 27,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,27; 76,38</t>
+          <t>29,04; 76,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,99; 73,17</t>
+          <t>29,9; 73,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,98; 62,04</t>
+          <t>16,83; 63,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,12; 54,11</t>
+          <t>9,84; 53,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,32; 49,67</t>
+          <t>26,16; 49,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28,38; 46,84</t>
+          <t>27,35; 46,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,97; 34,26</t>
+          <t>14,35; 34,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,65; 28,86</t>
+          <t>10,05; 29,06</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,69; 33,05</t>
+          <t>15,37; 33,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,9; 29,9</t>
+          <t>16,6; 29,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,11; 37,4</t>
+          <t>20,55; 37,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,83</t>
+          <t>6,47; 17,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,88; 48,78</t>
+          <t>18,45; 48,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,15; 38,59</t>
+          <t>18,88; 39,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,45; 42,82</t>
+          <t>21,56; 41,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,22; 35,59</t>
+          <t>18,17; 35,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,25; 32,88</t>
+          <t>18,28; 33,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,55; 30,4</t>
+          <t>19,11; 30,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,67; 36,49</t>
+          <t>23,61; 36,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,89; 22,94</t>
+          <t>13,03; 22,82</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,05; 31,26</t>
+          <t>16,71; 31,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,51; 33,96</t>
+          <t>16,54; 33,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,49; 24,42</t>
+          <t>11,39; 24,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 93,26</t>
+          <t>8,7; 94,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,44; 37,05</t>
+          <t>17,41; 36,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,17; 50,62</t>
+          <t>25,95; 50,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,41; 36,93</t>
+          <t>16,39; 36,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,68; 42,48</t>
+          <t>17,14; 42,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,08; 31,19</t>
+          <t>19,47; 31,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21,77; 35,92</t>
+          <t>22,31; 35,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15,16; 26,24</t>
+          <t>14,83; 26,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,87; 89,93</t>
+          <t>12,87; 91,55</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,43; 27,33</t>
+          <t>20,28; 27,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,74; 30,34</t>
+          <t>23,65; 30,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,94</t>
+          <t>20,09; 26,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,17; 70,28</t>
+          <t>14,27; 74,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,55; 43,81</t>
+          <t>31,47; 43,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,08; 41,17</t>
+          <t>31,07; 41,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,9; 36,43</t>
+          <t>26,98; 36,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,19; 30,87</t>
+          <t>22,8; 31,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24,84; 30,81</t>
+          <t>24,6; 30,87</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27,37; 32,66</t>
+          <t>27,33; 32,53</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23,61; 29,11</t>
+          <t>23,76; 29,03</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,35; 66,72</t>
+          <t>18,47; 65,18</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar hace menos tiempo (3.374 años)</t>
+          <t>Población que dejo de fumar hace menos tiempo (3.374 años) (tasa de respuesta: 96,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7069; 18106</t>
+          <t>7243; 18987</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17579; 34552</t>
+          <t>17485; 35159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14540; 31148</t>
+          <t>14825; 31608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4484; 15001</t>
+          <t>4458; 14562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6158; 15622</t>
+          <t>5950; 15227</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8587; 21844</t>
+          <t>9272; 23480</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11625; 26892</t>
+          <t>11843; 26313</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1044; 5207</t>
+          <t>1039; 5083</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15508; 31133</t>
+          <t>15402; 31104</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29299; 51756</t>
+          <t>30131; 52573</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29915; 53128</t>
+          <t>29810; 52072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6889; 17822</t>
+          <t>6765; 18144</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18469; 35795</t>
+          <t>17686; 35491</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23618; 43038</t>
+          <t>24138; 43540</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16663; 32770</t>
+          <t>16898; 33482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11834; 33039</t>
+          <t>12975; 33437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9110; 18922</t>
+          <t>8811; 18758</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18761; 35888</t>
+          <t>19254; 35766</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7663; 19532</t>
+          <t>7658; 19573</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11016; 24195</t>
+          <t>10659; 23875</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30154; 51506</t>
+          <t>30194; 52632</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47221; 74091</t>
+          <t>47177; 74302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27701; 47816</t>
+          <t>27691; 48772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27126; 52445</t>
+          <t>27835; 51902</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4712; 16725</t>
+          <t>4744; 17285</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16235; 32555</t>
+          <t>15639; 31873</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9329; 23109</t>
+          <t>9485; 22818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9795; 23407</t>
+          <t>9750; 23254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2967; 10743</t>
+          <t>2909; 10788</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8184; 20464</t>
+          <t>8169; 19914</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6318; 16731</t>
+          <t>6493; 16878</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9933; 21334</t>
+          <t>9471; 21278</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9905; 25034</t>
+          <t>9686; 25187</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27722; 47698</t>
+          <t>26964; 47713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18383; 35111</t>
+          <t>18567; 35738</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22694; 39658</t>
+          <t>23094; 40670</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11072; 26221</t>
+          <t>11369; 25583</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18314; 35343</t>
+          <t>17887; 36006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12970; 30084</t>
+          <t>12511; 29383</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6578; 22525</t>
+          <t>6690; 23172</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7796; 18830</t>
+          <t>7759; 18737</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10597; 23359</t>
+          <t>10341; 22738</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7088; 19998</t>
+          <t>7271; 19724</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8717; 18790</t>
+          <t>9240; 19260</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21376; 40146</t>
+          <t>21721; 40630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30595; 52769</t>
+          <t>31946; 53898</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22655; 43080</t>
+          <t>22603; 44448</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18731; 37535</t>
+          <t>18031; 37272</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5156; 16909</t>
+          <t>4955; 16534</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9685; 23663</t>
+          <t>9859; 23318</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6417; 18403</t>
+          <t>6897; 19778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1125; 6057</t>
+          <t>1097; 5999</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6512; 17343</t>
+          <t>6722; 17239</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4964; 14905</t>
+          <t>4926; 14709</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5251; 14343</t>
+          <t>5999; 14543</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>436; 4462</t>
+          <t>424; 4268</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14195; 30300</t>
+          <t>14724; 29969</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17348; 34126</t>
+          <t>17520; 34430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14246; 29222</t>
+          <t>14700; 29563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2457; 8454</t>
+          <t>2287; 8322</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10414; 24706</t>
+          <t>10421; 23818</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20938; 38075</t>
+          <t>19608; 36684</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4170; 15079</t>
+          <t>4037; 15371</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3066; 13053</t>
+          <t>2895; 12543</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4456; 13468</t>
+          <t>5120; 13466</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6553; 15987</t>
+          <t>6532; 16133</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2852; 10423</t>
+          <t>2828; 10657</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>674; 5965</t>
+          <t>1085; 5918</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18797; 34177</t>
+          <t>18002; 34341</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30336; 50066</t>
+          <t>29236; 49955</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9403; 23058</t>
+          <t>9658; 22918</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5443; 16277</t>
+          <t>5668; 16389</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13180; 29650</t>
+          <t>13787; 29895</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28512; 50446</t>
+          <t>28000; 50574</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27686; 49049</t>
+          <t>26945; 48545</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8282; 21914</t>
+          <t>7949; 21367</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4831; 14840</t>
+          <t>5613; 14887</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17583; 35437</t>
+          <t>17337; 35888</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19568; 37328</t>
+          <t>18796; 35862</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16876; 32968</t>
+          <t>16832; 32880</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>20726; 39497</t>
+          <t>21965; 40228</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50920; 79188</t>
+          <t>49789; 79568</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51682; 79676</t>
+          <t>51549; 79699</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27780; 49456</t>
+          <t>28091; 49186</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23279; 42671</t>
+          <t>22806; 42931</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21161; 43535</t>
+          <t>21210; 42330</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15863; 33720</t>
+          <t>15725; 33692</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28905; 322926</t>
+          <t>30108; 326157</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12781; 27161</t>
+          <t>12765; 27099</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16599; 33390</t>
+          <t>17119; 33093</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13740; 30917</t>
+          <t>13721; 30832</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6126; 15597</t>
+          <t>6295; 15545</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>40032; 65451</t>
+          <t>40846; 66046</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>42267; 69734</t>
+          <t>43325; 69024</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33623; 58186</t>
+          <t>32888; 59530</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49304; 344400</t>
+          <t>49304; 350605</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>125205; 167489</t>
+          <t>124287; 166633</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>196522; 251189</t>
+          <t>195806; 249507</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141854; 187411</t>
+          <t>139744; 186942</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119283; 591810</t>
+          <t>120136; 630142</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>78394; 108845</t>
+          <t>78185; 108434</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>121547; 161016</t>
+          <t>121524; 162416</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>102930; 139379</t>
+          <t>103228; 140116</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>73655; 102448</t>
+          <t>75678; 105035</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>213945; 265436</t>
+          <t>211891; 265948</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>333682; 398064</t>
+          <t>333130; 396541</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>254596; 313914</t>
+          <t>256191; 312961</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>215406; 783181</t>
+          <t>216793; 765163</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q25_A_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q25_A_R3-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,23; 42,56</t>
+          <t>14,78; 40,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 43,88</t>
+          <t>22,71; 43,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,36; 39,15</t>
+          <t>17,71; 39,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 31,64</t>
+          <t>12,89; 34,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,64; 75,86</t>
+          <t>30,76; 78,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,16; 58,65</t>
+          <t>23,21; 56,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,6; 47,99</t>
+          <t>21,87; 47,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,59; 42,05</t>
+          <t>11,21; 48,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 48,08</t>
+          <t>23,85; 47,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,08; 43,76</t>
+          <t>25,33; 43,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,99; 38,41</t>
+          <t>22,24; 38,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 31,23</t>
+          <t>14,1; 34,99</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,82; 31,75</t>
+          <t>15,59; 32,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 35,35</t>
+          <t>19,37; 36,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,12; 39,87</t>
+          <t>19,72; 39,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 30,98</t>
+          <t>11,65; 28,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,08; 72,55</t>
+          <t>34,61; 73,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,14; 55,99</t>
+          <t>28,76; 54,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,62; 50,14</t>
+          <t>19,41; 48,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,7; 37,41</t>
+          <t>18,09; 39,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,94; 38,24</t>
+          <t>21,79; 38,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,22; 39,72</t>
+          <t>25,54; 40,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,51; 39,65</t>
+          <t>22,35; 38,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,21; 30,22</t>
+          <t>14,91; 28,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 27,53</t>
+          <t>7,91; 27,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,62; 35,9</t>
+          <t>17,91; 36,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,05; 33,79</t>
+          <t>13,94; 33,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,59; 34,79</t>
+          <t>14,83; 35,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 75,78</t>
+          <t>21,07; 77,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,86; 58,17</t>
+          <t>22,67; 57,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,34; 55,48</t>
+          <t>20,85; 54,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,13; 42,99</t>
+          <t>20,33; 42,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,57; 32,7</t>
+          <t>12,8; 31,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,92; 38,79</t>
+          <t>22,53; 39,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,96; 36,49</t>
+          <t>19,45; 36,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,85; 34,96</t>
+          <t>20,12; 35,05</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,98; 33,71</t>
+          <t>14,77; 33,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 34,49</t>
+          <t>17,17; 33,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 29,74</t>
+          <t>12,32; 28,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 25,22</t>
+          <t>6,65; 23,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,98; 48,25</t>
+          <t>19,84; 47,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,24; 48,91</t>
+          <t>22,57; 51,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 38,9</t>
+          <t>15,61; 39,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 33,33</t>
+          <t>17,07; 36,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 35,42</t>
+          <t>18,55; 35,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 35,72</t>
+          <t>20,41; 35,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,12; 29,73</t>
+          <t>15,34; 29,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 24,9</t>
+          <t>12,39; 24,96</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,24; 40,85</t>
+          <t>12,75; 40,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,94; 47,17</t>
+          <t>20,32; 47,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,39; 44,13</t>
+          <t>15,08; 43,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 40,5</t>
+          <t>7,58; 39,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,91; 61,31</t>
+          <t>23,9; 60,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,35; 54,78</t>
+          <t>15,17; 52,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,08; 72,92</t>
+          <t>28,34; 75,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 51,27</t>
+          <t>4,88; 56,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,47; 43,69</t>
+          <t>21,02; 44,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,96; 45,13</t>
+          <t>23,12; 44,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,7; 45,65</t>
+          <t>22,27; 45,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,88; 35,97</t>
+          <t>10,25; 37,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,37; 46,54</t>
+          <t>20,06; 47,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,06; 43,13</t>
+          <t>24,39; 43,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,99; 30,43</t>
+          <t>9,34; 29,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 27,64</t>
+          <t>6,73; 26,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,04; 76,37</t>
+          <t>28,92; 76,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,9; 73,84</t>
+          <t>30,12; 73,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,83; 63,43</t>
+          <t>16,56; 62,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,84; 53,68</t>
+          <t>9,84; 53,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,16; 49,91</t>
+          <t>27,51; 50,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27,35; 46,73</t>
+          <t>28,22; 46,51</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,35; 34,05</t>
+          <t>15,05; 35,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,05; 29,06</t>
+          <t>9,76; 28,36</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,37; 33,32</t>
+          <t>15,06; 32,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,6; 29,98</t>
+          <t>16,59; 29,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,55; 37,01</t>
+          <t>20,87; 36,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 17,38</t>
+          <t>7,07; 19,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,45; 48,93</t>
+          <t>18,48; 48,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,88; 39,09</t>
+          <t>19,03; 38,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,56; 41,14</t>
+          <t>21,53; 42,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,17; 35,49</t>
+          <t>18,61; 36,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,28; 33,48</t>
+          <t>17,85; 33,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,11; 30,54</t>
+          <t>19,86; 30,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,61; 36,5</t>
+          <t>23,64; 36,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,03; 22,82</t>
+          <t>13,84; 23,66</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,71; 31,45</t>
+          <t>16,7; 31,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,54; 33,02</t>
+          <t>16,42; 32,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,39; 24,4</t>
+          <t>11,07; 24,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,7; 94,2</t>
+          <t>6,21; 17,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,41; 36,97</t>
+          <t>16,87; 36,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,95; 50,17</t>
+          <t>26,54; 51,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,39; 36,83</t>
+          <t>15,9; 37,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,14; 42,33</t>
+          <t>15,91; 41,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,47; 31,48</t>
+          <t>18,65; 30,73</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22,31; 35,55</t>
+          <t>21,8; 35,46</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,83; 26,84</t>
+          <t>14,74; 25,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,87; 91,55</t>
+          <t>10,78; 21,42</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,28; 27,19</t>
+          <t>20,69; 27,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,14</t>
+          <t>23,85; 30,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20,09; 26,88</t>
+          <t>20,46; 26,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,27; 74,84</t>
+          <t>12,74; 18,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,47; 43,64</t>
+          <t>31,96; 44,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,07; 41,53</t>
+          <t>31,47; 41,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,98; 36,62</t>
+          <t>26,9; 36,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22,8; 31,65</t>
+          <t>23,0; 31,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24,6; 30,87</t>
+          <t>24,84; 30,98</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27,33; 32,53</t>
+          <t>27,45; 33,11</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23,76; 29,03</t>
+          <t>23,52; 29,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,47; 65,18</t>
+          <t>17,13; 22,23</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>14167</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7243; 18987</t>
+          <t>6596; 17978</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17485; 35159</t>
+          <t>18193; 34498</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14825; 31608</t>
+          <t>14301; 31613</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4458; 14562</t>
+          <t>6334; 17052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5950; 15227</t>
+          <t>6174; 15777</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9272; 23480</t>
+          <t>9293; 22487</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11843; 26313</t>
+          <t>11993; 26130</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1039; 5083</t>
+          <t>1394; 5988</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15402; 31104</t>
+          <t>15426; 30602</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30131; 52573</t>
+          <t>30436; 51936</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29810; 52072</t>
+          <t>30155; 52401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6765; 18144</t>
+          <t>8682; 21542</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16780</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>39044</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17686; 35491</t>
+          <t>17430; 36192</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24138; 43540</t>
+          <t>23859; 44528</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16898; 33482</t>
+          <t>16563; 33214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12975; 33437</t>
+          <t>13542; 33531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8811; 18758</t>
+          <t>8948; 18991</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19254; 35766</t>
+          <t>18372; 34882</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7658; 19573</t>
+          <t>7576; 19035</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10659; 23875</t>
+          <t>11765; 25726</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30194; 52632</t>
+          <t>29991; 53055</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47177; 74302</t>
+          <t>47768; 75378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27691; 48772</t>
+          <t>27495; 47410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27835; 51902</t>
+          <t>27026; 52062</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15111</t>
+          <t>15178</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>31112</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4744; 17285</t>
+          <t>4968; 17338</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15639; 31873</t>
+          <t>15897; 32464</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9485; 22818</t>
+          <t>9416; 22826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9750; 23254</t>
+          <t>9755; 23354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2909; 10788</t>
+          <t>2999; 11076</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8169; 19914</t>
+          <t>7762; 19720</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6493; 16878</t>
+          <t>6343; 16659</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9471; 21278</t>
+          <t>10092; 20947</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9686; 25187</t>
+          <t>9859; 24034</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26964; 47713</t>
+          <t>27707; 48636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18567; 35738</t>
+          <t>19055; 35692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23094; 40670</t>
+          <t>23223; 40457</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>30912</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11369; 25583</t>
+          <t>11210; 25476</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17887; 36006</t>
+          <t>17923; 34992</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12511; 29383</t>
+          <t>12166; 27967</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6690; 23172</t>
+          <t>6956; 24526</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7759; 18737</t>
+          <t>7705; 18437</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10341; 22738</t>
+          <t>10492; 23714</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7271; 19724</t>
+          <t>7915; 20225</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9240; 19260</t>
+          <t>11039; 23638</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21721; 40630</t>
+          <t>21279; 40584</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31946; 53898</t>
+          <t>30800; 53336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22603; 44448</t>
+          <t>22934; 44279</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18031; 37272</t>
+          <t>20977; 42268</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5197</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4955; 16534</t>
+          <t>5161; 16533</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9859; 23318</t>
+          <t>10045; 23670</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6897; 19778</t>
+          <t>6760; 19561</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1097; 5999</t>
+          <t>1190; 6165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6722; 17239</t>
+          <t>6720; 17018</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4926; 14709</t>
+          <t>4073; 14197</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5999; 14543</t>
+          <t>5652; 14977</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>424; 4268</t>
+          <t>431; 4997</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14724; 29969</t>
+          <t>14418; 30648</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17520; 34430</t>
+          <t>17641; 34285</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14700; 29563</t>
+          <t>14420; 29624</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2287; 8322</t>
+          <t>2514; 9282</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>9247</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10421; 23818</t>
+          <t>10267; 24080</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19608; 36684</t>
+          <t>20745; 37398</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4037; 15371</t>
+          <t>4717; 14960</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2895; 12543</t>
+          <t>2997; 11907</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5120; 13466</t>
+          <t>5099; 13470</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6532; 16133</t>
+          <t>6580; 16027</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2828; 10657</t>
+          <t>2782; 10492</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1085; 5918</t>
+          <t>1131; 6168</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18002; 34341</t>
+          <t>18925; 34798</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>29236; 49955</t>
+          <t>30168; 49722</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9658; 22918</t>
+          <t>10132; 23659</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5668; 16389</t>
+          <t>5469; 15893</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>37833</t>
+          <t>44629</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13787; 29895</t>
+          <t>13511; 29300</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28000; 50574</t>
+          <t>27985; 49367</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26945; 48545</t>
+          <t>27377; 47882</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7949; 21367</t>
+          <t>10151; 28332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5613; 14887</t>
+          <t>5623; 14647</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17337; 35888</t>
+          <t>17469; 35370</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18796; 35862</t>
+          <t>18768; 36910</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16832; 32880</t>
+          <t>19551; 38042</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21965; 40228</t>
+          <t>21446; 39990</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49789; 79568</t>
+          <t>51744; 79756</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>51549; 79699</t>
+          <t>51619; 79422</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28091; 49186</t>
+          <t>34403; 58809</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>254685</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10331</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>265016</t>
+          <t>23878</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22806; 42931</t>
+          <t>22794; 43203</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21210; 42330</t>
+          <t>21046; 42032</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>15725; 33692</t>
+          <t>15286; 33519</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30108; 326157</t>
+          <t>7055; 19915</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12765; 27099</t>
+          <t>12366; 26629</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17119; 33093</t>
+          <t>17507; 33995</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13721; 30832</t>
+          <t>13312; 31454</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6295; 15545</t>
+          <t>6803; 17940</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>40846; 66046</t>
+          <t>39141; 64484</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43325; 69024</t>
+          <t>42324; 68850</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>32888; 59530</t>
+          <t>32697; 56665</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49304; 350605</t>
+          <t>16856; 33486</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>336115</t>
+          <t>101413</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>87565</t>
+          <t>96772</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>423679</t>
+          <t>198185</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>124287; 166633</t>
+          <t>126793; 168183</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>195806; 249507</t>
+          <t>197477; 249396</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>139744; 186942</t>
+          <t>142331; 187264</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120136; 630142</t>
+          <t>83236; 122653</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>78185; 108434</t>
+          <t>79418; 109802</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>121524; 162416</t>
+          <t>123096; 161109</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>103228; 140116</t>
+          <t>102934; 138426</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>75678; 105035</t>
+          <t>82780; 113518</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>211891; 265948</t>
+          <t>213966; 266848</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>333130; 396541</t>
+          <t>334545; 403641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>256191; 312961</t>
+          <t>253555; 313815</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>216793; 765163</t>
+          <t>173504; 225223</t>
         </is>
       </c>
     </row>
